--- a/hk0001.xlsx
+++ b/hk0001.xlsx
@@ -28,7 +28,7 @@
     <t xml:space="preserve">price</t>
   </si>
   <si>
-    <t xml:space="preserve">Qty.</t>
+    <t xml:space="preserve">qty</t>
   </si>
   <si>
     <t xml:space="preserve">2023/03/13</t>
